--- a/extracted_data.xlsx
+++ b/extracted_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="91">
   <si>
     <t>شناسه</t>
   </si>
@@ -34,6 +34,15 @@
     <t>تاریخ استخراج</t>
   </si>
   <si>
+    <t>دانش پويان هوش مصنوعي پارت</t>
+  </si>
+  <si>
+    <t>استحكام سازه يوز</t>
+  </si>
+  <si>
+    <t>بازرگاني طرح نو محمد</t>
+  </si>
+  <si>
     <t>كارا زمين سهند</t>
   </si>
   <si>
@@ -64,6 +73,21 @@
     <t>افشار ابزار طلايه</t>
   </si>
   <si>
+    <t>مهندسان سازه هاي ماندگار آرين مهر هفتم</t>
+  </si>
+  <si>
+    <t>آبادگران پاراك دشتگل</t>
+  </si>
+  <si>
+    <t>23151</t>
+  </si>
+  <si>
+    <t>11665</t>
+  </si>
+  <si>
+    <t>7562</t>
+  </si>
+  <si>
     <t>1893</t>
   </si>
   <si>
@@ -94,6 +118,42 @@
     <t>3450</t>
   </si>
   <si>
+    <t>2900</t>
+  </si>
+  <si>
+    <t>6493</t>
+  </si>
+  <si>
+    <t>4420591927</t>
+  </si>
+  <si>
+    <t>4430643441</t>
+  </si>
+  <si>
+    <t>4220170601</t>
+  </si>
+  <si>
+    <t>4220192875</t>
+  </si>
+  <si>
+    <t>4220326431</t>
+  </si>
+  <si>
+    <t>2432175255</t>
+  </si>
+  <si>
+    <t>4220203826</t>
+  </si>
+  <si>
+    <t>1990293107</t>
+  </si>
+  <si>
+    <t>1990887554</t>
+  </si>
+  <si>
+    <t>2000600921</t>
+  </si>
+  <si>
     <t>6369036870</t>
   </si>
   <si>
@@ -124,9 +184,66 @@
     <t>1910151165</t>
   </si>
   <si>
+    <t>1754880932</t>
+  </si>
+  <si>
+    <t>1990671251</t>
+  </si>
+  <si>
+    <t>0077911873</t>
+  </si>
+  <si>
+    <t>2739185162</t>
+  </si>
+  <si>
+    <t>2739179881</t>
+  </si>
+  <si>
+    <t>6360001500</t>
+  </si>
+  <si>
+    <t>1818461269</t>
+  </si>
+  <si>
+    <t>3380380441</t>
+  </si>
+  <si>
+    <t>3381037641</t>
+  </si>
+  <si>
+    <t>4699699197</t>
+  </si>
+  <si>
+    <t>1960386409</t>
+  </si>
+  <si>
     <t>مدیرعامل</t>
   </si>
   <si>
+    <t>رئیس هیئت مدیره</t>
+  </si>
+  <si>
+    <t>نایب رئیس هیئت مدیره</t>
+  </si>
+  <si>
+    <t>بازرس اصلی</t>
+  </si>
+  <si>
+    <t>بازرس علی البدل</t>
+  </si>
+  <si>
+    <t>عضو هیئت مدیره</t>
+  </si>
+  <si>
+    <t>2025-05-01 10:55:05</t>
+  </si>
+  <si>
+    <t>2025-05-01 10:55:06</t>
+  </si>
+  <si>
+    <t>2025-05-01 10:55:07</t>
+  </si>
+  <si>
     <t>2025-05-01 11:00:41</t>
   </si>
   <si>
@@ -155,6 +272,21 @@
   </si>
   <si>
     <t>2025-05-01 11:01:09</t>
+  </si>
+  <si>
+    <t>2025-05-01 11:21:56</t>
+  </si>
+  <si>
+    <t>2025-05-01 11:21:57</t>
+  </si>
+  <si>
+    <t>2025-05-01 11:26:29</t>
+  </si>
+  <si>
+    <t>2025-05-01 11:26:30</t>
+  </si>
+  <si>
+    <t>2025-05-01 11:28:21</t>
   </si>
 </sst>
 </file>
@@ -512,7 +644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -537,202 +669,622 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="F2" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="F3" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="F7" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
         <v>22</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="F8" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
         <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="F9" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="F10" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" t="s">
+        <v>67</v>
+      </c>
+      <c r="F13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" t="s">
+        <v>67</v>
+      </c>
+      <c r="F14" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" t="s">
+        <v>67</v>
+      </c>
+      <c r="F16" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" t="s">
+        <v>67</v>
+      </c>
+      <c r="F19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" t="s">
+        <v>67</v>
+      </c>
+      <c r="F20" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="B21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" t="s">
+        <v>67</v>
+      </c>
+      <c r="F21" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" t="s">
+        <v>56</v>
+      </c>
+      <c r="E22" t="s">
+        <v>70</v>
+      </c>
+      <c r="F22" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" t="s">
+        <v>57</v>
+      </c>
+      <c r="E23" t="s">
+        <v>71</v>
+      </c>
+      <c r="F23" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" t="s">
+        <v>58</v>
+      </c>
+      <c r="E24" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" t="s">
+        <v>59</v>
+      </c>
+      <c r="E25" t="s">
+        <v>68</v>
+      </c>
+      <c r="F25" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26">
         <v>25</v>
       </c>
-      <c r="D11" t="s">
+      <c r="B26" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" t="s">
+        <v>60</v>
+      </c>
+      <c r="E26" t="s">
+        <v>70</v>
+      </c>
+      <c r="F26" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" t="s">
+        <v>61</v>
+      </c>
+      <c r="E27" t="s">
+        <v>68</v>
+      </c>
+      <c r="F27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" t="s">
+        <v>62</v>
+      </c>
+      <c r="E28" t="s">
+        <v>69</v>
+      </c>
+      <c r="F28" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" t="s">
+        <v>63</v>
+      </c>
+      <c r="E29" t="s">
+        <v>72</v>
+      </c>
+      <c r="F29" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" t="s">
+        <v>64</v>
+      </c>
+      <c r="E30" t="s">
+        <v>71</v>
+      </c>
+      <c r="F30" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" t="s">
+        <v>65</v>
+      </c>
+      <c r="E31" t="s">
+        <v>70</v>
+      </c>
+      <c r="F31" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" t="s">
         <v>35</v>
       </c>
-      <c r="E11" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" t="s">
-        <v>46</v>
+      <c r="D32" t="s">
+        <v>66</v>
+      </c>
+      <c r="E32" t="s">
+        <v>68</v>
+      </c>
+      <c r="F32" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
